--- a/2026.1/EPC - Estatística e Probabilidade para Computação/pt2_analise_explor_CPC_2021_lic_musica_LIMPO.xlsx
+++ b/2026.1/EPC - Estatística e Probabilidade para Computação/pt2_analise_explor_CPC_2021_lic_musica_LIMPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guilh\Documents\# UNICAP\Aulas-UNICAP\2026.1\EPC - Estatística e Probabilidade para Computação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23EC71BA-19BC-41CC-8244-810B848BD90B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1694B36-18E0-4DFB-A19B-58C4BC9CCC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="662" firstSheet="1" activeTab="3" xr2:uid="{AD14C073-7BDC-4576-B930-9EB3B3B004BE}"/>
   </bookViews>
@@ -18,11 +18,17 @@
     <sheet name="Análise (desorganizada)" sheetId="2" r:id="rId3"/>
     <sheet name="Análise (organizada)" sheetId="5" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">'Análise (desorganizada)'!$C$15</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'Análise (desorganizada)'!$C$16:$C$113</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'Análise (desorganizada)'!$C$15</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'Análise (desorganizada)'!$C$16:$C$113</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId5"/>
     <pivotCache cacheId="1" r:id="rId6"/>
-    <pivotCache cacheId="9" r:id="rId7"/>
+    <pivotCache cacheId="2" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -44,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="58">
   <si>
     <t>Ano</t>
   </si>
@@ -186,6 +192,39 @@
   <si>
     <t>Aqui e nos 2 gráficos seguintes, tentamos verificar a hipótese anterior. É possível afirmar que os cursos presenciais possuem nota maior em geral.</t>
   </si>
+  <si>
+    <t>Métrica</t>
+  </si>
+  <si>
+    <t>Resultado</t>
+  </si>
+  <si>
+    <t>Quantidade de Cursos</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Mediana</t>
+  </si>
+  <si>
+    <t>Máximo</t>
+  </si>
+  <si>
+    <t>Mínimo</t>
+  </si>
+  <si>
+    <t>Desvio Padrão</t>
+  </si>
+  <si>
+    <t>Tabela com estatísticas sobre nota de conhecimentos específicos</t>
+  </si>
+  <si>
+    <t>Quantidade</t>
+  </si>
+  <si>
+    <t>Desvio_Padrão</t>
+  </si>
 </sst>
 </file>
 
@@ -194,7 +233,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,8 +256,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -237,8 +282,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -276,6 +327,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -295,26 +361,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -29974,6 +30044,62 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="107"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -30349,6 +30475,142 @@
     </c:ext>
   </c:extLst>
 </c:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.1</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Box-plot NOTACE</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+            </a:rPr>
+            <a:t>Box-plot NOTACE</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{4918069B-1F0E-47FE-A309-5A794B4EECEB}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.0</cx:f>
+              <cx:v>NOTACE</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling min="30"/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx2.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.3</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Box-plot NOTACE</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+            </a:rPr>
+            <a:t>Box-plot NOTACE</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{4918069B-1F0E-47FE-A309-5A794B4EECEB}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.2</cx:f>
+              <cx:v>NOTACE</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling min="30"/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -30911,6 +31173,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors22.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors23.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -32701,6 +33043,521 @@
 </file>
 
 <file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -33203,7 +34060,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -33722,7 +34579,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -34238,7 +35095,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style16.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -34741,7 +35598,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style17.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -35244,7 +36101,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style18.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -35747,7 +36604,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style19.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -36250,8 +37107,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style19.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -36308,7 +37165,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -36359,6 +37216,13 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -36369,12 +37233,19 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -36412,7 +37283,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -36455,22 +37326,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -36575,8 +37447,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -36708,19 +37580,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -36753,8 +37626,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<file path=xl/charts/style20.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -36811,7 +37684,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -36862,13 +37735,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -36879,19 +37745,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -36929,7 +37788,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -36972,23 +37831,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -37093,8 +37951,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -37226,20 +38084,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -37272,7 +38129,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style21.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -37775,7 +38632,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style22.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -38274,6 +39131,521 @@
         <a:noFill/>
       </a:ln>
     </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style23.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -42210,6 +43582,84 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>30479</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>125037</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>205740</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>143741</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="6" name="Chart 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE760728-14B0-AD5B-E99D-686DB05E70B4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3901439" y="11494077"/>
+              <a:ext cx="3855721" cy="2761904"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -42369,13 +43819,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
+      <xdr:col>44</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>42</xdr:col>
+      <xdr:col>51</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>175260</xdr:rowOff>
@@ -42407,13 +43857,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>43</xdr:col>
+      <xdr:col>52</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>55</xdr:col>
+      <xdr:col>64</xdr:col>
       <xdr:colOff>264795</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>96203</xdr:rowOff>
@@ -42445,13 +43895,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>56</xdr:col>
+      <xdr:col>65</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>67</xdr:col>
+      <xdr:col>76</xdr:col>
       <xdr:colOff>480060</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
@@ -42483,13 +43933,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>69</xdr:col>
+      <xdr:col>78</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>179797</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>81</xdr:col>
+      <xdr:col>90</xdr:col>
       <xdr:colOff>325348</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>128426</xdr:rowOff>
@@ -42521,16 +43971,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>82</xdr:col>
-      <xdr:colOff>68494</xdr:colOff>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>83734</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>39211</xdr:rowOff>
+      <xdr:rowOff>16351</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>89</xdr:col>
-      <xdr:colOff>565079</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>5584</xdr:rowOff>
+      <xdr:col>97</xdr:col>
+      <xdr:colOff>397439</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>165604</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -42559,13 +44009,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>93</xdr:col>
+      <xdr:col>98</xdr:col>
       <xdr:colOff>44173</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>58317</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>103</xdr:col>
+      <xdr:col>108</xdr:col>
       <xdr:colOff>69858</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>169000</xdr:rowOff>
@@ -42593,6 +44043,84 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="Chart 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20CC9B55-661B-47C8-9149-B773B58F039A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="21381720" y="739140"/>
+              <a:ext cx="5951220" cy="3261360"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -45259,7 +46787,1092 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DC177230-6FD0-48D1-9B5E-E06037E632B6}" name="PivotTable8" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F337217-9431-47DF-8567-C687D120C07D}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="P69:V73" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="49" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of MODALID" fld="4" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="10">
+    <chartFormat chart="5" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{214E4D23-E0BE-488F-B9DB-95E643EABDFD}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="TOTAL" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="MODALID">
+  <location ref="B2:C5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Contagem de IES" fld="3" subtotal="count" baseField="5" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{809346AA-8EB5-4BEE-A66F-5ED337B13EA9}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="S2:V9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="49" showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="95">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="4"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of NOTACE" fld="2" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="16">
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="106" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="109" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="110" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="109" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="110" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="107" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8363D68D-7605-4EAE-BF5A-86062AC124C6}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+  <location ref="P41:V48" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="49" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of CATADM" fld="3" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="10">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{92D1C496-E786-4DE5-A51C-A1CD8501B2C6}" name="PivotTable15" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="P17:Q23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="49" showAll="0" defaultSubtotal="0">
+      <items count="87">
+        <item x="30"/>
+        <item x="53"/>
+        <item x="7"/>
+        <item x="41"/>
+        <item x="31"/>
+        <item x="36"/>
+        <item x="55"/>
+        <item x="78"/>
+        <item x="33"/>
+        <item x="70"/>
+        <item x="60"/>
+        <item x="77"/>
+        <item x="11"/>
+        <item x="21"/>
+        <item x="32"/>
+        <item x="81"/>
+        <item x="79"/>
+        <item x="82"/>
+        <item x="84"/>
+        <item x="61"/>
+        <item x="38"/>
+        <item x="48"/>
+        <item x="67"/>
+        <item x="27"/>
+        <item x="63"/>
+        <item x="22"/>
+        <item x="62"/>
+        <item x="16"/>
+        <item x="34"/>
+        <item x="15"/>
+        <item x="6"/>
+        <item x="83"/>
+        <item x="8"/>
+        <item x="72"/>
+        <item x="17"/>
+        <item x="25"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="85"/>
+        <item x="12"/>
+        <item x="74"/>
+        <item x="46"/>
+        <item x="69"/>
+        <item x="43"/>
+        <item x="20"/>
+        <item x="66"/>
+        <item x="49"/>
+        <item x="19"/>
+        <item x="73"/>
+        <item x="76"/>
+        <item x="59"/>
+        <item x="54"/>
+        <item x="65"/>
+        <item x="71"/>
+        <item x="86"/>
+        <item x="37"/>
+        <item x="68"/>
+        <item x="50"/>
+        <item x="10"/>
+        <item x="40"/>
+        <item x="52"/>
+        <item x="13"/>
+        <item x="24"/>
+        <item x="51"/>
+        <item x="58"/>
+        <item x="64"/>
+        <item x="44"/>
+        <item x="42"/>
+        <item x="35"/>
+        <item x="80"/>
+        <item x="9"/>
+        <item x="14"/>
+        <item x="18"/>
+        <item x="29"/>
+        <item x="0"/>
+        <item x="56"/>
+        <item x="75"/>
+        <item x="23"/>
+        <item x="26"/>
+        <item x="2"/>
+        <item x="39"/>
+        <item x="28"/>
+        <item x="5"/>
+        <item x="57"/>
+        <item x="45"/>
+        <item x="4"/>
+        <item x="47"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Categoria" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="10">
+    <chartFormat chart="0" format="87" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="88">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="89">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="90">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="91">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="97" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="98">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="99">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="100">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="101">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DC177230-6FD0-48D1-9B5E-E06037E632B6}" name="PivotTable8" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="Z2:AA5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField showAll="0"/>
@@ -45451,8 +48064,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B357F506-F7F5-402A-8F96-D192FC11F57F}" name="PivotTable7" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B357F506-F7F5-402A-8F96-D192FC11F57F}" name="PivotTable7" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="S26:T32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField showAll="0"/>
@@ -45737,131 +48350,37 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{809346AA-8EB5-4BEE-A66F-5ED337B13EA9}" name="PivotTable6" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
-  <location ref="S2:V9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="5">
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E9DCB33D-A828-4629-9061-6F3F5F44637E}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="TOTAL" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="CATADM">
+  <location ref="B7:C13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
     <pivotField showAll="0"/>
-    <pivotField numFmtId="49" showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="95">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
         <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
         <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" showAll="0">
+    <pivotField showAll="0">
       <items count="3">
         <item x="1"/>
         <item x="0"/>
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="3"/>
+    <field x="4"/>
   </rowFields>
   <rowItems count="6">
     <i>
@@ -45883,187 +48402,12 @@
       <x/>
     </i>
   </rowItems>
-  <colFields count="1">
-    <field x="4"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
+  <colItems count="1">
+    <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Average of NOTACE" fld="2" subtotal="average" baseField="0" baseItem="0"/>
+    <dataField name="Contagem de IES" fld="3" subtotal="count" baseField="5" baseItem="0"/>
   </dataFields>
-  <chartFormats count="15">
-    <chartFormat chart="0" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="9" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="10" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="11" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="106" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="109" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="110" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="109" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="110" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -46076,8 +48420,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7F998D38-6A41-4A76-83D4-385344A43888}" name="PivotTable5" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7F998D38-6A41-4A76-83D4-385344A43888}" name="PivotTable5" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="P91:S98" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField showAll="0">
@@ -46200,810 +48544,6 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F337217-9431-47DF-8567-C687D120C07D}" name="PivotTable4" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="P69:V73" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="49" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of MODALID" fld="4" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="10">
-    <chartFormat chart="5" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="10" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="11" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="12" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="13" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="14" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8363D68D-7605-4EAE-BF5A-86062AC124C6}" name="PivotTable3" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
-  <location ref="P41:V48" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="49" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of CATADM" fld="3" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="10">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="10" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="11" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="12" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="13" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="14" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{214E4D23-E0BE-488F-B9DB-95E643EABDFD}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="TOTAL" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="MODALID">
-  <location ref="B2:C5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Contagem de IES" fld="3" subtotal="count" baseField="5" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{92D1C496-E786-4DE5-A51C-A1CD8501B2C6}" name="PivotTable15" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="P17:Q23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="49" showAll="0" defaultSubtotal="0">
-      <items count="87">
-        <item x="30"/>
-        <item x="53"/>
-        <item x="7"/>
-        <item x="41"/>
-        <item x="31"/>
-        <item x="36"/>
-        <item x="55"/>
-        <item x="78"/>
-        <item x="33"/>
-        <item x="70"/>
-        <item x="60"/>
-        <item x="77"/>
-        <item x="11"/>
-        <item x="21"/>
-        <item x="32"/>
-        <item x="81"/>
-        <item x="79"/>
-        <item x="82"/>
-        <item x="84"/>
-        <item x="61"/>
-        <item x="38"/>
-        <item x="48"/>
-        <item x="67"/>
-        <item x="27"/>
-        <item x="63"/>
-        <item x="22"/>
-        <item x="62"/>
-        <item x="16"/>
-        <item x="34"/>
-        <item x="15"/>
-        <item x="6"/>
-        <item x="83"/>
-        <item x="8"/>
-        <item x="72"/>
-        <item x="17"/>
-        <item x="25"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="85"/>
-        <item x="12"/>
-        <item x="74"/>
-        <item x="46"/>
-        <item x="69"/>
-        <item x="43"/>
-        <item x="20"/>
-        <item x="66"/>
-        <item x="49"/>
-        <item x="19"/>
-        <item x="73"/>
-        <item x="76"/>
-        <item x="59"/>
-        <item x="54"/>
-        <item x="65"/>
-        <item x="71"/>
-        <item x="86"/>
-        <item x="37"/>
-        <item x="68"/>
-        <item x="50"/>
-        <item x="10"/>
-        <item x="40"/>
-        <item x="52"/>
-        <item x="13"/>
-        <item x="24"/>
-        <item x="51"/>
-        <item x="58"/>
-        <item x="64"/>
-        <item x="44"/>
-        <item x="42"/>
-        <item x="35"/>
-        <item x="80"/>
-        <item x="9"/>
-        <item x="14"/>
-        <item x="18"/>
-        <item x="29"/>
-        <item x="0"/>
-        <item x="56"/>
-        <item x="75"/>
-        <item x="23"/>
-        <item x="26"/>
-        <item x="2"/>
-        <item x="39"/>
-        <item x="28"/>
-        <item x="5"/>
-        <item x="57"/>
-        <item x="45"/>
-        <item x="4"/>
-        <item x="47"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Categoria" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="10">
-    <chartFormat chart="0" format="87" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="88">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="89">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="90">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="91">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="97" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="98">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="99">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="100">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="101">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E9DCB33D-A828-4629-9061-6F3F5F44637E}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="TOTAL" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="CATADM">
-  <location ref="B7:C13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Contagem de IES" fld="3" subtotal="count" baseField="5" baseItem="0"/>
-  </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -53450,10 +54990,10 @@
       <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="9" t="s">
         <v>20</v>
       </c>
       <c r="S2" s="3" t="s">
@@ -53476,10 +55016,10 @@
       <c r="C3">
         <v>10</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="9">
         <v>10</v>
       </c>
       <c r="S3" s="3" t="s">
@@ -53497,7 +55037,7 @@
       <c r="Z3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AA3" s="7">
+      <c r="AA3">
         <v>41.116250000000001</v>
       </c>
     </row>
@@ -53508,28 +55048,28 @@
       <c r="C4">
         <v>88</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="9">
         <v>88</v>
       </c>
       <c r="S4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="T4" s="7">
+      <c r="T4">
         <v>39.265500000000003</v>
       </c>
-      <c r="U4" s="7">
+      <c r="U4">
         <v>40.263750000000002</v>
       </c>
-      <c r="V4" s="7">
+      <c r="V4">
         <v>39.931000000000004</v>
       </c>
       <c r="Z4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AA4" s="7">
+      <c r="AA4">
         <v>47.8018</v>
       </c>
     </row>
@@ -53540,28 +55080,28 @@
       <c r="C5">
         <v>98</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="9">
         <v>98</v>
       </c>
       <c r="S5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="7">
+      <c r="T5">
         <v>42.181000000000004</v>
       </c>
-      <c r="U5" s="7">
+      <c r="U5">
         <v>48.582550000000012</v>
       </c>
-      <c r="V5" s="7">
+      <c r="V5">
         <v>47.515625</v>
       </c>
       <c r="Z5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="AA5" s="7">
+      <c r="AA5">
         <v>47.226698924731188</v>
       </c>
     </row>
@@ -53569,13 +55109,13 @@
       <c r="S6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="T6" s="7">
+      <c r="T6">
         <v>33.332999999999998</v>
       </c>
-      <c r="U6" s="7">
+      <c r="U6">
         <v>48.101157894736843</v>
       </c>
-      <c r="V6" s="7">
+      <c r="V6">
         <v>47.362750000000005</v>
       </c>
     </row>
@@ -53589,13 +55129,13 @@
       <c r="S7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="T7" s="7">
+      <c r="T7">
         <v>48.341999999999999</v>
       </c>
-      <c r="U7" s="7">
+      <c r="U7">
         <v>48.08558536585366</v>
       </c>
-      <c r="V7" s="7">
+      <c r="V7">
         <v>48.091690476190479</v>
       </c>
     </row>
@@ -53609,11 +55149,10 @@
       <c r="S8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7">
+      <c r="U8">
         <v>45.015999999999998</v>
       </c>
-      <c r="V8" s="7">
+      <c r="V8">
         <v>45.015999999999998</v>
       </c>
     </row>
@@ -53627,13 +55166,13 @@
       <c r="S9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="T9" s="7">
+      <c r="T9">
         <v>41.116250000000001</v>
       </c>
-      <c r="U9" s="7">
+      <c r="U9">
         <v>47.801799999999993</v>
       </c>
-      <c r="V9" s="7">
+      <c r="V9">
         <v>47.226698924731188</v>
       </c>
     </row>
@@ -53670,7 +55209,7 @@
       </c>
     </row>
     <row r="14" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="2:27" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>2</v>
       </c>
@@ -53989,7 +55528,7 @@
       <c r="S27" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="T27" s="7">
+      <c r="T27">
         <v>39.931000000000004</v>
       </c>
     </row>
@@ -54018,7 +55557,7 @@
       <c r="S28" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="T28" s="7">
+      <c r="T28">
         <v>47.515625</v>
       </c>
     </row>
@@ -54047,7 +55586,7 @@
       <c r="S29" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="7">
+      <c r="T29">
         <v>47.362750000000005</v>
       </c>
     </row>
@@ -54076,7 +55615,7 @@
       <c r="S30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="T30" s="7">
+      <c r="T30">
         <v>48.091690476190479</v>
       </c>
     </row>
@@ -54105,7 +55644,7 @@
       <c r="S31" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="T31" s="7">
+      <c r="T31">
         <v>45.015999999999998</v>
       </c>
     </row>
@@ -54134,7 +55673,7 @@
       <c r="S32" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="T32" s="7">
+      <c r="T32">
         <v>47.226698924731167</v>
       </c>
     </row>
@@ -54306,10 +55845,10 @@
       <c r="C40" s="2">
         <v>42.826000000000001</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E40" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" s="9" t="s">
         <v>20</v>
       </c>
       <c r="J40" t="s">
@@ -54335,10 +55874,10 @@
       <c r="C41" s="2">
         <v>42.896999999999998</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F41" s="11">
+      <c r="F41" s="9">
         <v>6</v>
       </c>
       <c r="J41" t="s">
@@ -54370,10 +55909,10 @@
       <c r="C42" s="2">
         <v>42.975999999999999</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E42" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F42" s="11">
+      <c r="F42" s="9">
         <v>24</v>
       </c>
       <c r="J42" t="s">
@@ -54420,10 +55959,10 @@
       <c r="C43" s="2">
         <v>43.043999999999997</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E43" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="11">
+      <c r="F43" s="9">
         <v>22</v>
       </c>
       <c r="J43" t="s">
@@ -54444,16 +55983,13 @@
       <c r="P43" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="Q43" s="7">
+      <c r="Q43">
         <v>3</v>
       </c>
-      <c r="R43" s="7">
+      <c r="R43">
         <v>3</v>
       </c>
-      <c r="S43" s="7"/>
-      <c r="T43" s="7"/>
-      <c r="U43" s="7"/>
-      <c r="V43" s="7">
+      <c r="V43">
         <v>6</v>
       </c>
     </row>
@@ -54464,10 +56000,10 @@
       <c r="C44" s="2">
         <v>43.057000000000002</v>
       </c>
-      <c r="E44" s="11" t="s">
+      <c r="E44" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F44" s="11">
+      <c r="F44" s="9">
         <v>44</v>
       </c>
       <c r="J44" t="s">
@@ -54488,20 +56024,19 @@
       <c r="P44" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="Q44" s="7">
+      <c r="Q44">
         <v>3</v>
       </c>
-      <c r="R44" s="7">
+      <c r="R44">
         <v>13</v>
       </c>
-      <c r="S44" s="7">
+      <c r="S44">
         <v>6</v>
       </c>
-      <c r="T44" s="7">
+      <c r="T44">
         <v>2</v>
       </c>
-      <c r="U44" s="7"/>
-      <c r="V44" s="7">
+      <c r="V44">
         <v>24</v>
       </c>
     </row>
@@ -54512,10 +56047,10 @@
       <c r="C45" s="2">
         <v>43.140999999999998</v>
       </c>
-      <c r="E45" s="11" t="s">
+      <c r="E45" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F45" s="11">
+      <c r="F45" s="9">
         <v>2</v>
       </c>
       <c r="J45" t="s">
@@ -54536,22 +56071,22 @@
       <c r="P45" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="7">
+      <c r="Q45">
         <v>3</v>
       </c>
-      <c r="R45" s="7">
+      <c r="R45">
         <v>11</v>
       </c>
-      <c r="S45" s="7">
+      <c r="S45">
         <v>3</v>
       </c>
-      <c r="T45" s="7">
+      <c r="T45">
         <v>3</v>
       </c>
-      <c r="U45" s="7">
+      <c r="U45">
         <v>2</v>
       </c>
-      <c r="V45" s="7">
+      <c r="V45">
         <v>22</v>
       </c>
     </row>
@@ -54562,10 +56097,10 @@
       <c r="C46" s="2">
         <v>43.72</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E46" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F46" s="11">
+      <c r="F46" s="9">
         <v>98</v>
       </c>
       <c r="J46" t="s">
@@ -54586,20 +56121,19 @@
       <c r="P46" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="Q46" s="7">
+      <c r="Q46">
         <v>3</v>
       </c>
-      <c r="R46" s="7">
+      <c r="R46">
         <v>24</v>
       </c>
-      <c r="S46" s="7">
+      <c r="S46">
         <v>15</v>
       </c>
-      <c r="T46" s="7"/>
-      <c r="U46" s="7">
+      <c r="U46">
         <v>2</v>
       </c>
-      <c r="V46" s="7">
+      <c r="V46">
         <v>44</v>
       </c>
     </row>
@@ -54628,16 +56162,13 @@
       <c r="P47" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="Q47" s="7"/>
-      <c r="R47" s="7">
+      <c r="R47">
         <v>1</v>
       </c>
-      <c r="S47" s="7"/>
-      <c r="T47" s="7"/>
-      <c r="U47" s="7">
+      <c r="U47">
         <v>1</v>
       </c>
-      <c r="V47" s="7">
+      <c r="V47">
         <v>2</v>
       </c>
     </row>
@@ -54666,22 +56197,22 @@
       <c r="P48" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="Q48" s="7">
+      <c r="Q48">
         <v>12</v>
       </c>
-      <c r="R48" s="7">
+      <c r="R48">
         <v>52</v>
       </c>
-      <c r="S48" s="7">
+      <c r="S48">
         <v>24</v>
       </c>
-      <c r="T48" s="7">
+      <c r="T48">
         <v>5</v>
       </c>
-      <c r="U48" s="7">
+      <c r="U48">
         <v>5</v>
       </c>
-      <c r="V48" s="7">
+      <c r="V48">
         <v>98</v>
       </c>
     </row>
@@ -55243,18 +56774,16 @@
       <c r="P71" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="Q71" s="7">
+      <c r="Q71">
         <v>2</v>
       </c>
-      <c r="R71" s="7">
+      <c r="R71">
         <v>6</v>
       </c>
-      <c r="S71" s="7"/>
-      <c r="T71" s="7"/>
-      <c r="U71" s="7">
+      <c r="U71">
         <v>2</v>
       </c>
-      <c r="V71" s="7">
+      <c r="V71">
         <v>10</v>
       </c>
     </row>
@@ -55283,22 +56812,22 @@
       <c r="P72" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q72" s="7">
+      <c r="Q72">
         <v>10</v>
       </c>
-      <c r="R72" s="7">
+      <c r="R72">
         <v>46</v>
       </c>
-      <c r="S72" s="7">
+      <c r="S72">
         <v>24</v>
       </c>
-      <c r="T72" s="7">
+      <c r="T72">
         <v>5</v>
       </c>
-      <c r="U72" s="7">
+      <c r="U72">
         <v>3</v>
       </c>
-      <c r="V72" s="7">
+      <c r="V72">
         <v>88</v>
       </c>
     </row>
@@ -55327,22 +56856,22 @@
       <c r="P73" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="Q73" s="7">
+      <c r="Q73">
         <v>12</v>
       </c>
-      <c r="R73" s="7">
+      <c r="R73">
         <v>52</v>
       </c>
-      <c r="S73" s="7">
+      <c r="S73">
         <v>24</v>
       </c>
-      <c r="T73" s="7">
+      <c r="T73">
         <v>5</v>
       </c>
-      <c r="U73" s="7">
+      <c r="U73">
         <v>5</v>
       </c>
-      <c r="V73" s="7">
+      <c r="V73">
         <v>98</v>
       </c>
     </row>
@@ -55826,13 +57355,13 @@
       <c r="P93" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="Q93" s="7">
+      <c r="Q93">
         <v>2</v>
       </c>
-      <c r="R93" s="7">
+      <c r="R93">
         <v>4</v>
       </c>
-      <c r="S93" s="7">
+      <c r="S93">
         <v>6</v>
       </c>
     </row>
@@ -55861,13 +57390,13 @@
       <c r="P94" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="Q94" s="7">
+      <c r="Q94">
         <v>4</v>
       </c>
-      <c r="R94" s="7">
+      <c r="R94">
         <v>20</v>
       </c>
-      <c r="S94" s="7">
+      <c r="S94">
         <v>24</v>
       </c>
     </row>
@@ -55896,13 +57425,13 @@
       <c r="P95" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="Q95" s="7">
+      <c r="Q95">
         <v>1</v>
       </c>
-      <c r="R95" s="7">
+      <c r="R95">
         <v>21</v>
       </c>
-      <c r="S95" s="7">
+      <c r="S95">
         <v>22</v>
       </c>
     </row>
@@ -55931,13 +57460,13 @@
       <c r="P96" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="Q96" s="7">
+      <c r="Q96">
         <v>2</v>
       </c>
-      <c r="R96" s="7">
+      <c r="R96">
         <v>42</v>
       </c>
-      <c r="S96" s="7">
+      <c r="S96">
         <v>44</v>
       </c>
     </row>
@@ -55966,13 +57495,13 @@
       <c r="P97" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="Q97" s="7">
+      <c r="Q97">
         <v>1</v>
       </c>
-      <c r="R97" s="7">
+      <c r="R97">
         <v>1</v>
       </c>
-      <c r="S97" s="7">
+      <c r="S97">
         <v>2</v>
       </c>
     </row>
@@ -56001,13 +57530,13 @@
       <c r="P98" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="Q98" s="7">
+      <c r="Q98">
         <v>10</v>
       </c>
-      <c r="R98" s="7">
+      <c r="R98">
         <v>88</v>
       </c>
-      <c r="S98" s="7">
+      <c r="S98">
         <v>98</v>
       </c>
     </row>
@@ -56381,271 +57910,409 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A39EB34A-6FA9-4697-A24F-B03A895560FA}">
-  <dimension ref="B2:CY27"/>
+  <dimension ref="B2:DD33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="8.88671875" customWidth="1"/>
+    <col min="37" max="37" width="19.33203125" customWidth="1"/>
+    <col min="38" max="38" width="12.5546875" customWidth="1"/>
+    <col min="92" max="92" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:95" x14ac:dyDescent="0.3">
-      <c r="B2" s="12" t="s">
+    <row r="2" spans="2:100" x14ac:dyDescent="0.3">
+      <c r="B2" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="12"/>
+      <c r="C2" s="15"/>
     </row>
-    <row r="3" spans="2:95" x14ac:dyDescent="0.3">
-      <c r="B3" s="16" t="s">
+    <row r="3" spans="2:100" x14ac:dyDescent="0.3">
+      <c r="B3" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="K3" s="16" t="s">
+      <c r="C3" s="12"/>
+      <c r="K3" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="16"/>
-      <c r="R3" s="16" t="s">
+      <c r="L3" s="12"/>
+      <c r="R3" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="S3" s="16"/>
-      <c r="Y3" s="16" t="s">
+      <c r="S3" s="12"/>
+      <c r="Y3" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="Z3" s="16"/>
-      <c r="AJ3" s="16" t="s">
+      <c r="Z3" s="12"/>
+      <c r="AJ3" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="AK3" s="16"/>
-      <c r="AR3" s="16" t="s">
+      <c r="AK3" s="12"/>
+      <c r="AS3" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="AS3" s="16"/>
-      <c r="BE3" s="16" t="s">
+      <c r="AT3" s="12"/>
+      <c r="BA3" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="BF3" s="16"/>
-      <c r="BR3" s="16" t="s">
+      <c r="BB3" s="12"/>
+      <c r="BN3" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="BS3" s="16"/>
-      <c r="CE3" s="16" t="s">
+      <c r="BO3" s="12"/>
+      <c r="CA3" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="CF3" s="16"/>
-      <c r="CP3" s="16" t="s">
+      <c r="CB3" s="12"/>
+      <c r="CN3" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="CQ3" s="16"/>
+      <c r="CO3" s="12"/>
+      <c r="CU3" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="CV3" s="12"/>
     </row>
-    <row r="23" spans="2:103" x14ac:dyDescent="0.3">
-      <c r="B23" s="8"/>
+    <row r="24" spans="2:108" x14ac:dyDescent="0.3">
+      <c r="B24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="W24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AM24" s="7"/>
+      <c r="AN24" s="7"/>
+      <c r="AO24" s="7"/>
+      <c r="AP24" s="7"/>
+      <c r="AQ24" s="7"/>
+      <c r="AR24" s="7"/>
+      <c r="AU24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AX24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="BA24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="BG24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="BJ24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="BM24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="BP24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="BS24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="BV24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="BY24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="CB24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="CE24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="CH24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="CK24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="CN24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="CQ24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="CT24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="CW24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="CZ24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="DC24" s="7" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="24" spans="2:103" x14ac:dyDescent="0.3">
-      <c r="B24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="N24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="T24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="W24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="AL24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="AO24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="AR24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="AU24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="AX24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="BA24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="BD24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="BG24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="BJ24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="BM24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="BP24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="BS24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="BV24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="BY24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="CB24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="CE24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="CH24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="CK24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="CN24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="CQ24" s="9"/>
-      <c r="CT24" s="9"/>
-      <c r="CW24" s="9"/>
+    <row r="25" spans="2:108" x14ac:dyDescent="0.3">
+      <c r="AK25" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="26" spans="2:103" x14ac:dyDescent="0.3">
-      <c r="B26" s="14" t="s">
+    <row r="26" spans="2:108" x14ac:dyDescent="0.3">
+      <c r="B26" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
     </row>
-    <row r="27" spans="2:103" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="13" t="s">
+    <row r="27" spans="2:108" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="10" t="s">
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="K27" s="15" t="s">
+      <c r="K27" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="10" t="s">
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="13"/>
+      <c r="Q27" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="R27" s="15" t="s">
+      <c r="R27" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="S27" s="15"/>
-      <c r="T27" s="15"/>
-      <c r="U27" s="15"/>
-      <c r="V27" s="15"/>
-      <c r="W27" s="10" t="s">
+      <c r="S27" s="13"/>
+      <c r="T27" s="13"/>
+      <c r="U27" s="13"/>
+      <c r="V27" s="13"/>
+      <c r="W27" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="X27" s="15" t="s">
+      <c r="X27" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="Y27" s="15"/>
-      <c r="Z27" s="15"/>
-      <c r="AA27" s="15"/>
-      <c r="AB27" s="15"/>
-      <c r="AI27" s="10" t="s">
+      <c r="Y27" s="13"/>
+      <c r="Z27" s="13"/>
+      <c r="AA27" s="13"/>
+      <c r="AB27" s="13"/>
+      <c r="AI27" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="AJ27" s="15" t="s">
+      <c r="AK27" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL27" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AN27" s="8"/>
+      <c r="AO27" s="8"/>
+      <c r="AP27" s="8"/>
+      <c r="AQ27" s="8"/>
+      <c r="AR27" s="8"/>
+      <c r="AS27" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="AK27" s="15"/>
-      <c r="AL27" s="15"/>
-      <c r="AM27" s="15"/>
-      <c r="AN27" s="15"/>
-      <c r="AP27" s="10" t="s">
+      <c r="AT27" s="13"/>
+      <c r="AU27" s="13"/>
+      <c r="AV27" s="13"/>
+      <c r="AW27" s="13"/>
+      <c r="AY27" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="AR27" s="15" t="s">
+      <c r="BA27" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="AS27" s="15"/>
-      <c r="AT27" s="15"/>
-      <c r="AU27" s="15"/>
-      <c r="AV27" s="15"/>
-      <c r="BD27" s="10" t="s">
+      <c r="BB27" s="13"/>
+      <c r="BC27" s="13"/>
+      <c r="BD27" s="13"/>
+      <c r="BE27" s="13"/>
+      <c r="BM27" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="BE27" s="15" t="s">
+      <c r="BN27" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="BF27" s="15"/>
-      <c r="BG27" s="15"/>
-      <c r="BH27" s="15"/>
-      <c r="BI27" s="15"/>
-      <c r="BJ27" s="15"/>
-      <c r="BP27" s="10" t="s">
+      <c r="BO27" s="13"/>
+      <c r="BP27" s="13"/>
+      <c r="BQ27" s="13"/>
+      <c r="BR27" s="13"/>
+      <c r="BS27" s="13"/>
+      <c r="BY27" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="BR27" s="15" t="s">
+      <c r="CA27" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="BS27" s="15"/>
-      <c r="BT27" s="15"/>
-      <c r="BU27" s="15"/>
-      <c r="BV27" s="15"/>
-      <c r="BW27" s="15"/>
-      <c r="CD27" s="10"/>
-      <c r="CY27" s="10" t="s">
+      <c r="CB27" s="13"/>
+      <c r="CC27" s="13"/>
+      <c r="CD27" s="13"/>
+      <c r="CE27" s="13"/>
+      <c r="CF27" s="13"/>
+      <c r="CM27" s="8"/>
+      <c r="CN27" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="CO27" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="CP27" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="CQ27" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="CR27" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="CS27" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="CT27" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="DD27" s="8" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="2:108" x14ac:dyDescent="0.3">
+      <c r="AK28" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="AL28" s="11">
+        <v>93</v>
+      </c>
+      <c r="CN28" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="CO28" s="11">
+        <v>85</v>
+      </c>
+      <c r="CP28" s="11">
+        <v>47.8018</v>
+      </c>
+      <c r="CQ28" s="11">
+        <v>46.92</v>
+      </c>
+      <c r="CR28" s="11">
+        <v>67.3</v>
+      </c>
+      <c r="CS28" s="11">
+        <v>31.623000000000001</v>
+      </c>
+      <c r="CT28" s="11">
+        <v>7.3027892107839776</v>
+      </c>
+    </row>
+    <row r="29" spans="2:108" x14ac:dyDescent="0.3">
+      <c r="AK29" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL29" s="11">
+        <v>47.226698924731188</v>
+      </c>
+      <c r="CN29" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="CO29" s="11">
+        <v>8</v>
+      </c>
+      <c r="CP29" s="11">
+        <v>41.116250000000001</v>
+      </c>
+      <c r="CQ29" s="11">
+        <v>41.268500000000003</v>
+      </c>
+      <c r="CR29" s="11">
+        <v>48.341999999999999</v>
+      </c>
+      <c r="CS29" s="11">
+        <v>33.332999999999998</v>
+      </c>
+      <c r="CT29" s="11">
+        <v>4.3358648420553223</v>
+      </c>
+    </row>
+    <row r="30" spans="2:108" x14ac:dyDescent="0.3">
+      <c r="AK30" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="AL30" s="11">
+        <v>46.656999999999996</v>
+      </c>
+    </row>
+    <row r="31" spans="2:108" x14ac:dyDescent="0.3">
+      <c r="AK31" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="AL31" s="11">
+        <v>67.3</v>
+      </c>
+    </row>
+    <row r="32" spans="2:108" x14ac:dyDescent="0.3">
+      <c r="AK32" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="AL32" s="11">
+        <v>31.623000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="37:38" x14ac:dyDescent="0.3">
+      <c r="AK33" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="AL33" s="11">
+        <v>7.3263914716130829</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="CE3:CF3"/>
-    <mergeCell ref="BR3:BS3"/>
-    <mergeCell ref="CP3:CQ3"/>
-    <mergeCell ref="BE3:BF3"/>
-    <mergeCell ref="AR3:AS3"/>
+  <mergeCells count="21">
+    <mergeCell ref="CN3:CO3"/>
+    <mergeCell ref="CA3:CB3"/>
+    <mergeCell ref="CU3:CV3"/>
+    <mergeCell ref="BN3:BO3"/>
+    <mergeCell ref="BA3:BB3"/>
     <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="X27:AB27"/>
-    <mergeCell ref="AJ27:AN27"/>
-    <mergeCell ref="AR27:AV27"/>
-    <mergeCell ref="BE27:BJ27"/>
-    <mergeCell ref="BR27:BW27"/>
+    <mergeCell ref="BN27:BS27"/>
+    <mergeCell ref="CA27:CF27"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B26:D26"/>
@@ -56654,19 +58321,26 @@
     <mergeCell ref="R3:S3"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="B3:C3"/>
+    <mergeCell ref="AS3:AT3"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="X27:AB27"/>
+    <mergeCell ref="AS27:AW27"/>
+    <mergeCell ref="BA27:BE27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" location="'Análise (desorganizada)'!P91:S98" display="Tabela desse gráfico" xr:uid="{77A56FD5-5824-4890-AA46-E52307E26DC0}"/>
     <hyperlink ref="K3" location="'Análise (desorganizada)'!E40:F46" display="Tabela desse gráfico" xr:uid="{F3C40307-70D5-43E2-B81A-611A24F37E15}"/>
     <hyperlink ref="R3" location="'Análise (desorganizada)'!E2:F5" display="Tabela desse gráfico" xr:uid="{DFB3BAD0-4B5B-4DEB-B791-42613AF98651}"/>
     <hyperlink ref="Y3" location="'Análise (desorganizada)'!B15:C113" display="Tabela desse gráfico" xr:uid="{A62F3C0F-BA8E-4276-A50E-B42A5E292BFC}"/>
-    <hyperlink ref="AJ3" location="'Análise (desorganizada)'!P17:Q23" display="Tabela desse gráfico" xr:uid="{ACBD0835-20B9-4A8D-A457-6A6D9A6C79A0}"/>
-    <hyperlink ref="AR3" location="'Análise (desorganizada)'!P41:V48" display="Tabela desse gráfico" xr:uid="{5780F1D8-8F3E-4938-A22F-E9744C558E45}"/>
-    <hyperlink ref="BE3" location="'Análise (desorganizada)'!P69:V73" display="Tabela desse gráfico" xr:uid="{A1F661F9-A5C0-4137-9C73-ED8BC38EBEEF}"/>
-    <hyperlink ref="BR3" location="'Análise (desorganizada)'!S2:V9" display="Tabela desse gráfico" xr:uid="{EEB51255-FF24-42B1-A966-EFFD21141913}"/>
-    <hyperlink ref="CP3" location="'Análise (desorganizada)'!S2:V9" display="Tabela desse gráfico" xr:uid="{7F79AC84-1FAA-475D-B302-4AD93C0F7EC4}"/>
-    <hyperlink ref="CP3:CQ3" location="'Análise (desorganizada)'!S26:T32" display="Tabela desse gráfico" xr:uid="{1770E38E-B1FF-446E-9AE3-FAF5A7FC7C95}"/>
-    <hyperlink ref="CE3" location="'Análise (desorganizada)'!S2:V9" display="Tabela desse gráfico" xr:uid="{0EA430A6-4B83-4860-BB03-94D5E5D4B5CE}"/>
+    <hyperlink ref="AS3" location="'Análise (desorganizada)'!P17:Q23" display="Tabela desse gráfico" xr:uid="{ACBD0835-20B9-4A8D-A457-6A6D9A6C79A0}"/>
+    <hyperlink ref="BA3" location="'Análise (desorganizada)'!P41:V48" display="Tabela desse gráfico" xr:uid="{5780F1D8-8F3E-4938-A22F-E9744C558E45}"/>
+    <hyperlink ref="BN3" location="'Análise (desorganizada)'!P69:V73" display="Tabela desse gráfico" xr:uid="{A1F661F9-A5C0-4137-9C73-ED8BC38EBEEF}"/>
+    <hyperlink ref="CA3" location="'Análise (desorganizada)'!S2:V9" display="Tabela desse gráfico" xr:uid="{EEB51255-FF24-42B1-A966-EFFD21141913}"/>
+    <hyperlink ref="CU3" location="'Análise (desorganizada)'!S2:V9" display="Tabela desse gráfico" xr:uid="{7F79AC84-1FAA-475D-B302-4AD93C0F7EC4}"/>
+    <hyperlink ref="CU3:CV3" location="'Análise (desorganizada)'!S26:T32" display="Tabela desse gráfico" xr:uid="{1770E38E-B1FF-446E-9AE3-FAF5A7FC7C95}"/>
+    <hyperlink ref="CN3" location="'Análise (desorganizada)'!S2:V9" display="Tabela desse gráfico" xr:uid="{0EA430A6-4B83-4860-BB03-94D5E5D4B5CE}"/>
+    <hyperlink ref="AJ3" location="'Análise (desorganizada)'!P17:Q23" display="Tabela desse gráfico" xr:uid="{B696394F-E595-43CD-8109-90A4D0A5BAA2}"/>
+    <hyperlink ref="AJ3:AK3" location="'Análise (desorganizada)'!C15:C113" display="Tabela desse gráfico" xr:uid="{47D9CD2C-01D4-42E2-91A5-6BDD4AACEA3F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
